--- a/Java23 QuyenPhan Database Design.xlsx
+++ b/Java23 QuyenPhan Database Design.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java23\3. Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4166D1C-5EF2-4C74-AFDB-4D5D11213092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6E72B2-F137-42AA-BA8D-B2A4C5EFC114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="588" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="588" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
     <sheet name="B2. Mô hình logic" sheetId="5" r:id="rId2"/>
     <sheet name="B2. ERD - Mô hình logic" sheetId="2" r:id="rId3"/>
     <sheet name="B3. Mô hình quan hệ" sheetId="6" r:id="rId4"/>
-    <sheet name="RD - Mô hình quan hệ" sheetId="3" r:id="rId5"/>
-    <sheet name="DB - Mô hình vật lý" sheetId="4" r:id="rId6"/>
+    <sheet name="B4. Mô hình vật lý" sheetId="4" r:id="rId5"/>
+    <sheet name="RD - Mô hình quan hệ" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -214,8 +214,83 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D2762586-1568-4CA1-84B1-25C4A6B7BF3D}</author>
+    <author>tc={5BB71AC4-9659-4B49-AE00-20328F749FE8}</author>
+    <author>tc={B0B8351A-F8B3-4EDE-8A43-27DE73070A70}</author>
+    <author>tc={F97C4A89-C3BD-42B8-81A3-F88B0C7B2B49}</author>
+    <author>tc={6B85BF31-59E0-4C41-93B2-A52F1794EB43}</author>
+    <author>tc={757E2222-AC3E-4A43-98F1-5381EF486FA8}</author>
+  </authors>
+  <commentList>
+    <comment ref="K6" authorId="0" shapeId="0" xr:uid="{D2762586-1568-4CA1-84B1-25C4A6B7BF3D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Khách
+Nhân Viên
+Quản Lý 
+Giám Đốc</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="1" shapeId="0" xr:uid="{5BB71AC4-9659-4B49-AE00-20328F749FE8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Chờ xử lý
+Đã xử lý, chờ đóng gói
+Đang đóng gói
+Đang giao hàng
+Giao hàng thành công
+Giao hàng thất bại
+Hủy đơn hàng</t>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="2" shapeId="0" xr:uid="{B0B8351A-F8B3-4EDE-8A43-27DE73070A70}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Thanh toán khi nhận hàng
+Thanh toán online - chuyển khoản
+Thanh toán online - thẻ ghi nợ
+</t>
+      </text>
+    </comment>
+    <comment ref="Q7" authorId="3" shapeId="0" xr:uid="{F97C4A89-C3BD-42B8-81A3-F88B0C7B2B49}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng bán của mặt hàng trong đơn hàng</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="4" shapeId="0" xr:uid="{6B85BF31-59E0-4C41-93B2-A52F1794EB43}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng tồn kho theo mặt hàng, kích cỡ</t>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="5" shapeId="0" xr:uid="{757E2222-AC3E-4A43-98F1-5381EF486FA8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Người tạo</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="455">
   <si>
     <t>MatHang</t>
   </si>
@@ -533,18 +608,6 @@
   </si>
   <si>
     <t>Z</t>
-  </si>
-  <si>
-    <t>1. Tạo table đúng thứ tự hoặc sau đó sẽ alter table thêm ràng buộc</t>
-  </si>
-  <si>
-    <t>2. Tạo dữ liệu thì phải tạo cho bảng 1 trước. Bảng nhiều sau</t>
-  </si>
-  <si>
-    <t>Mất thời gian</t>
-  </si>
-  <si>
-    <t>Disable constraint FK …..</t>
   </si>
   <si>
     <r>
@@ -1354,12 +1417,415 @@
   <si>
     <t>- Lưu ý: Dữ liệu trong cột khóa ngoại có thể trùng nhau để đảm bảo mối liên kết 1-n</t>
   </si>
+  <si>
+    <t>1. Database</t>
+  </si>
+  <si>
+    <t>2. Tables</t>
+  </si>
+  <si>
+    <t>3. Columns</t>
+  </si>
+  <si>
+    <t>-- View, Function, Procedure, Index, Trigger, Partition</t>
+  </si>
+  <si>
+    <t>java23_shopping</t>
+  </si>
+  <si>
+    <t>T01_ITEM</t>
+  </si>
+  <si>
+    <t>C01_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C01_ITEM_NAME</t>
+  </si>
+  <si>
+    <t>4. Constraints: Primary, Foreign Keys, Unique, NOT NULL, IN SET</t>
+  </si>
+  <si>
+    <t>Áo sơ mi</t>
+  </si>
+  <si>
+    <t>Quần jean</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>T02_SIZE</t>
+  </si>
+  <si>
+    <t>C02_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C02_SIZE_NAME</t>
+  </si>
+  <si>
+    <t>T03_ITEM_DETAIL kết hợp của ITEM và SIZE</t>
+  </si>
+  <si>
+    <t>C03_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C02_GENDER</t>
+  </si>
+  <si>
+    <t>C02_SIZE_DESC</t>
+  </si>
+  <si>
+    <t>Size S - Nu - Từ 40 đến 50kg</t>
+  </si>
+  <si>
+    <t>Size S - Nam - Từ 45 đến 55kg</t>
+  </si>
+  <si>
+    <t>T03_ITEM_DETAIL</t>
+  </si>
+  <si>
+    <t>N N</t>
+  </si>
+  <si>
+    <t>Khóa chính này có 2 columns, được tham chiếu từ table khác</t>
+  </si>
+  <si>
+    <t>Bảng tham chiếu sẽ cần có 2 columns này</t>
+  </si>
+  <si>
+    <t>UNIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         : Thêm ràng buộc unique cho 2 columns pk cũ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Xử lý:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tạo column mới làm khóa chính đại diện cho table</t>
+    </r>
+  </si>
+  <si>
+    <t>C03_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C03_SALES_PRICE</t>
+  </si>
+  <si>
+    <t>T04_ITEM_GROUP</t>
+  </si>
+  <si>
+    <t>C04_ITEM_GROUP_ID</t>
+  </si>
+  <si>
+    <t>C04_ITEM_GROUP_NAME</t>
+  </si>
+  <si>
+    <t>C01_ITEM_GROUP_ID</t>
+  </si>
+  <si>
+    <t>C03_COLOR</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>T05_GALLERY</t>
+  </si>
+  <si>
+    <t>C05_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C05_COLOR</t>
+  </si>
+  <si>
+    <t>C05_IMAGE</t>
+  </si>
+  <si>
+    <t>file://img01</t>
+  </si>
+  <si>
+    <t>file://img02</t>
+  </si>
+  <si>
+    <t>file://img03</t>
+  </si>
+  <si>
+    <t>C03_AMOUNT</t>
+  </si>
+  <si>
+    <t>T06_ORDER</t>
+  </si>
+  <si>
+    <t>C06_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C06_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C06_RECEIVER_NAME</t>
+  </si>
+  <si>
+    <t>C06_RECEIVER_PHONE</t>
+  </si>
+  <si>
+    <t>C06_DELIVERY_ADDRESS</t>
+  </si>
+  <si>
+    <t>C06_ORDER_TIME</t>
+  </si>
+  <si>
+    <t>T07_CUSTOMER</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_NAME</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_PHONE</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_EMAIL</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_GENDER</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_DOB</t>
+  </si>
+  <si>
+    <t>C07_CUSTOMER_ADDRESS</t>
+  </si>
+  <si>
+    <t>C09_ACCOUNT_ID</t>
+  </si>
+  <si>
+    <t>T09_ACCOUNT</t>
+  </si>
+  <si>
+    <t>C09_USERNAME</t>
+  </si>
+  <si>
+    <t>C09_PASSWORD</t>
+  </si>
+  <si>
+    <t>C09_ACCOUNT_STATUS</t>
+  </si>
+  <si>
+    <t>C07_ACCOUNT_ID</t>
+  </si>
+  <si>
+    <t>C09_ROLE_ID</t>
+  </si>
+  <si>
+    <t>T10_ROLE</t>
+  </si>
+  <si>
+    <t>C10_ROLE_ID</t>
+  </si>
+  <si>
+    <t>C10_ROLE_NAME</t>
+  </si>
+  <si>
+    <t>T11_ORDER_STATUS</t>
+  </si>
+  <si>
+    <t>C11_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C11_ORDER_STATUS_DESC</t>
+  </si>
+  <si>
+    <t>T12_ORDER_STATUS_DETAIL</t>
+  </si>
+  <si>
+    <t>C12_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C12_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C12_EMPLOYE_ID</t>
+  </si>
+  <si>
+    <t>C12_LAST_UPDATED</t>
+  </si>
+  <si>
+    <t>Chờ xử lý</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Đang giao</t>
+  </si>
+  <si>
+    <t>NV4</t>
+  </si>
+  <si>
+    <t>NV6</t>
+  </si>
+  <si>
+    <t>Giao thành công</t>
+  </si>
+  <si>
+    <t>T13_PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>C13_PAYMENT_METHOD_ID</t>
+  </si>
+  <si>
+    <t>C13_PAYMENT_METHOD_NAME</t>
+  </si>
+  <si>
+    <t>C06_PAYMENT_METHOD_ID</t>
+  </si>
+  <si>
+    <t>C06_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C12_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>T08_EMPLOYEE</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_NAME</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_PHONE</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_EMAIL</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_GENDER</t>
+  </si>
+  <si>
+    <t>C08_EMPLOYEE_DOB</t>
+  </si>
+  <si>
+    <t>C08_ACCOUNT_ID</t>
+  </si>
+  <si>
+    <t>C08_TITLE_ID</t>
+  </si>
+  <si>
+    <t>T14_TITLE</t>
+  </si>
+  <si>
+    <t>C14_TITLE_ID</t>
+  </si>
+  <si>
+    <t>C14_TITLE_NAME</t>
+  </si>
+  <si>
+    <t>T15_BILL</t>
+  </si>
+  <si>
+    <t>C15_BILL_ID</t>
+  </si>
+  <si>
+    <t>C15_DELIVERY_FEE</t>
+  </si>
+  <si>
+    <t>C15_TOTAL_OF_MONEY</t>
+  </si>
+  <si>
+    <t>C15_ORDER_ID</t>
+  </si>
+  <si>
+    <t>Tìm những đơn hàng bị hủy</t>
+  </si>
+  <si>
+    <t>T16_ITEM_DETAIL</t>
+  </si>
+  <si>
+    <t>C16_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C03_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C16_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C16_AMOUNT</t>
+  </si>
+  <si>
+    <t>T19_PROVIDER</t>
+  </si>
+  <si>
+    <t>C19_PROVIDER_ID</t>
+  </si>
+  <si>
+    <t>C19_PROVIDER_NAME</t>
+  </si>
+  <si>
+    <t>C19_PROVIDER_TAX</t>
+  </si>
+  <si>
+    <t>Phiếu Nhập Hàng</t>
+  </si>
+  <si>
+    <t>T17_ITEM_RECEIVED_NOTE</t>
+  </si>
+  <si>
+    <t>C17_IRN_ID</t>
+  </si>
+  <si>
+    <t>C17_IRN_TIME</t>
+  </si>
+  <si>
+    <t>C17_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C18_BUY_PRICE</t>
+  </si>
+  <si>
+    <t>C18_IRN_ID</t>
+  </si>
+  <si>
+    <t>C18_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C18_AMOUNT</t>
+  </si>
+  <si>
+    <t>C18_PROVIDER_ID</t>
+  </si>
+  <si>
+    <t>T18_ITEM_RECEIVED_NOTE_DETAIL</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1390,30 +1856,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1494,8 +1937,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1556,6 +2035,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1601,10 +2086,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1635,17 +2121,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1679,23 +2156,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1719,8 +2196,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1729,26 +2206,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1768,15 +2252,57 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1792,53 +2318,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>360217</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>70090</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>188992</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>46068</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6295796" y="4712274"/>
-          <a:ext cx="2716354" cy="1239294"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Quyen Ngoc Phan" id="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" userId="S::Quyen.Ngoc.Phan@mgm-tp.com::a07336a7-4c4c-48f3-ae7a-f1af5b9df94c" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2102,6 +2585,41 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K6" dT="2025-03-02T14:20:09.75" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{D2762586-1568-4CA1-84B1-25C4A6B7BF3D}">
+    <text>Khách
+Nhân Viên
+Quản Lý 
+Giám Đốc</text>
+  </threadedComment>
+  <threadedComment ref="L6" dT="2025-03-02T14:26:35.13" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{5BB71AC4-9659-4B49-AE00-20328F749FE8}">
+    <text>Chờ xử lý
+Đã xử lý, chờ đóng gói
+Đang đóng gói
+Đang giao hàng
+Giao hàng thành công
+Giao hàng thất bại
+Hủy đơn hàng</text>
+  </threadedComment>
+  <threadedComment ref="N6" dT="2025-03-02T14:35:08.08" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{B0B8351A-F8B3-4EDE-8A43-27DE73070A70}">
+    <text xml:space="preserve">Thanh toán khi nhận hàng
+Thanh toán online - chuyển khoản
+Thanh toán online - thẻ ghi nợ
+</text>
+  </threadedComment>
+  <threadedComment ref="Q7" dT="2025-03-02T14:49:39.98" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{F97C4A89-C3BD-42B8-81A3-F88B0C7B2B49}">
+    <text>Số lượng bán của mặt hàng trong đơn hàng</text>
+  </threadedComment>
+  <threadedComment ref="D10" dT="2025-03-02T14:03:38.33" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{6B85BF31-59E0-4C41-93B2-A52F1794EB43}">
+    <text>Số lượng tồn kho theo mặt hàng, kích cỡ</text>
+  </threadedComment>
+  <threadedComment ref="G12" dT="2025-03-02T14:36:28.94" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{757E2222-AC3E-4A43-98F1-5381EF486FA8}">
+    <text>Người tạo</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:L24"/>
@@ -2124,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -2139,19 +2657,19 @@
         <v>13</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2164,69 +2682,69 @@
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="50" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="53" t="s">
-        <v>257</v>
+      <c r="B6" s="50" t="s">
+        <v>253</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="50" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L6" s="53" t="s">
-        <v>250</v>
+        <v>249</v>
+      </c>
+      <c r="L6" s="50" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -2239,132 +2757,132 @@
         <v>17</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="53" t="s">
-        <v>229</v>
+      <c r="B9" s="50" t="s">
+        <v>225</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="53" t="s">
-        <v>256</v>
+      <c r="B10" s="50" t="s">
+        <v>252</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="53" t="s">
-        <v>233</v>
+      <c r="D10" s="50" t="s">
+        <v>229</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="53" t="s">
-        <v>247</v>
+      <c r="J10" s="50" t="s">
+        <v>243</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="53" t="s">
-        <v>255</v>
+      <c r="B11" s="50" t="s">
+        <v>251</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="53" t="s">
-        <v>247</v>
+      <c r="D11" s="50" t="s">
+        <v>243</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="G11" s="53" t="s">
-        <v>240</v>
+      <c r="F11" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>236</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="53" t="s">
-        <v>254</v>
+      <c r="B12" s="50" t="s">
+        <v>250</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="H12" s="53"/>
+      <c r="G12" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="H12" s="50"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2476,11 +2994,11 @@
       <c r="L20" s="2"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" s="18" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B22" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="15" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2507,8 +3025,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F2" s="18" t="s">
-        <v>303</v>
+      <c r="F2" s="15" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2516,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -2534,110 +3052,110 @@
         <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="M4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="N5" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="55" t="s">
+      <c r="O5" s="52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F6" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="I5" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="J5" s="55" t="s">
-        <v>241</v>
-      </c>
-      <c r="K5" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="L5" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="M5" s="55" t="s">
-        <v>305</v>
-      </c>
-      <c r="N5" s="55" t="s">
-        <v>252</v>
-      </c>
-      <c r="O5" s="55" t="s">
+      <c r="G6" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="53" t="s">
-        <v>257</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>14</v>
@@ -2645,7 +3163,7 @@
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -2655,56 +3173,56 @@
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="53" t="s">
-        <v>247</v>
+      <c r="K7" s="50" t="s">
+        <v>243</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>229</v>
+        <v>255</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>225</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="E8" s="53" t="s">
+      <c r="D8" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="50" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2716,70 +3234,70 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="53" t="s">
-        <v>256</v>
+      <c r="B9" s="50" t="s">
+        <v>252</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="53" t="s">
-        <v>248</v>
+      <c r="L9" s="50" t="s">
+        <v>244</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="53" t="s">
-        <v>255</v>
+      <c r="B10" s="50" t="s">
+        <v>251</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="53"/>
+      <c r="D10" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" s="50"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="53" t="s">
-        <v>254</v>
+      <c r="B11" s="50" t="s">
+        <v>250</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="E11" s="53"/>
+      <c r="D11" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="E11" s="50"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="H11" s="53" t="s">
-        <v>240</v>
+      <c r="G11" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>236</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -2798,10 +3316,10 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="I12" s="53"/>
+      <c r="H12" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="I12" s="50"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -2952,33 +3470,33 @@
         <v>13</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" s="18" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" s="15" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24" t="s">
         <v>71</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
-      <c r="H24" s="53" t="s">
+      <c r="H24" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="I24" s="53" t="s">
+      <c r="I24" s="50" t="s">
         <v>1</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N24" s="53" t="s">
-        <v>261</v>
+      <c r="N24" s="50" t="s">
+        <v>257</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.25">
@@ -2988,26 +3506,26 @@
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
-      <c r="G25" s="56" t="s">
-        <v>280</v>
-      </c>
-      <c r="H25" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="I25" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="J25" s="47">
+      <c r="G25" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="H25" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" s="44">
         <v>2</v>
       </c>
-      <c r="N25" s="47" t="s">
-        <v>281</v>
-      </c>
-      <c r="O25" s="47" t="s">
+      <c r="N25" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="O25" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="P25" s="47" t="s">
-        <v>282</v>
+      <c r="P25" s="44" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.25">
@@ -3017,117 +3535,117 @@
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="I26" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="J26" s="47">
+      <c r="G26" s="53"/>
+      <c r="H26" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="I26" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="J26" s="44">
         <v>4</v>
       </c>
-      <c r="N26" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="O26" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="P26" s="47" t="s">
-        <v>285</v>
+      <c r="N26" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="O26" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="P26" s="44" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="56"/>
-      <c r="H27" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="I27" s="47" t="s">
-        <v>273</v>
-      </c>
-      <c r="J27" s="47">
+      <c r="G27" s="53"/>
+      <c r="H27" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="I27" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="J27" s="44">
         <v>1</v>
       </c>
-      <c r="N27" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="O27" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="P27" s="47" t="s">
-        <v>289</v>
+      <c r="N27" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="P27" s="44" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H28" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="I28" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="J28" s="47">
+      <c r="H28" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="J28" s="44">
         <v>2</v>
       </c>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
-      <c r="P28" s="47"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H29" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="I29" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="J29" s="47">
+      <c r="H29" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="I29" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="J29" s="44">
         <v>4</v>
       </c>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="G30" s="56" t="s">
-        <v>280</v>
-      </c>
-      <c r="H30" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="I30" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="J30" s="47">
+      <c r="G30" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="H30" s="48" t="s">
+        <v>266</v>
+      </c>
+      <c r="I30" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="J30" s="44">
         <v>8</v>
       </c>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="N31" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="O31" s="47"/>
-      <c r="P31" s="47"/>
+      <c r="N31" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="N32" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.25">
@@ -3135,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
@@ -3146,11 +3664,11 @@
         <v>2</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H35" s="53" t="s">
+      <c r="H35" s="50" t="s">
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -3163,15 +3681,15 @@
         <v>3</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H36" s="47" t="s">
-        <v>271</v>
+      <c r="H36" s="44" t="s">
+        <v>267</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J36" s="5">
         <v>100</v>
@@ -3180,301 +3698,301 @@
         <v>4</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H37" s="47" t="s">
-        <v>272</v>
+      <c r="H37" s="44" t="s">
+        <v>268</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J37" s="5">
         <v>200</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H38" s="47" t="s">
-        <v>273</v>
+      <c r="H38" s="44" t="s">
+        <v>269</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="J38" s="5">
         <v>220</v>
       </c>
       <c r="N38" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="N39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="N40" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="N41" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="N42" s="47" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
-      <c r="N39" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="47"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="47"/>
-      <c r="N40" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="47"/>
-      <c r="N41" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
-      <c r="N42" s="50" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
+        <v>295</v>
+      </c>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
       <c r="N43" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G44" s="47"/>
+        <v>244</v>
+      </c>
+      <c r="G44" s="44"/>
       <c r="N44" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="47" t="s">
-        <v>298</v>
-      </c>
-      <c r="C45" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="D45" s="47">
+      <c r="B45" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="D45" s="44">
         <v>200</v>
       </c>
-      <c r="E45" s="47">
+      <c r="E45" s="44">
         <v>15</v>
       </c>
-      <c r="F45" s="47" t="s">
+      <c r="F45" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="G45" s="47"/>
+      <c r="G45" s="44"/>
       <c r="N45" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="47" t="s">
-        <v>298</v>
-      </c>
-      <c r="C46" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="D46" s="47">
+      <c r="B46" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="D46" s="44">
         <v>120</v>
       </c>
-      <c r="E46" s="47">
+      <c r="E46" s="44">
         <v>12</v>
       </c>
-      <c r="F46" s="47" t="s">
+      <c r="F46" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="G46" s="47"/>
+      <c r="G46" s="44"/>
       <c r="N46" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="47" t="s">
-        <v>298</v>
-      </c>
-      <c r="C47" s="47" t="s">
-        <v>273</v>
-      </c>
-      <c r="D47" s="47">
+      <c r="B47" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="D47" s="44">
         <v>400</v>
       </c>
-      <c r="E47" s="47">
+      <c r="E47" s="44">
         <v>10</v>
       </c>
-      <c r="F47" s="47" t="s">
+      <c r="F47" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="G47" s="47"/>
+      <c r="G47" s="44"/>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
+      <c r="B50" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D51" s="50" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D51" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="47" t="s">
-        <v>298</v>
-      </c>
-      <c r="C52" s="52">
+      <c r="B52" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="C52" s="49">
         <v>18.02</v>
       </c>
-      <c r="D52" s="47" t="s">
+      <c r="D52" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="C53" s="52">
+      <c r="B53" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="C53" s="49">
         <v>18.02</v>
       </c>
-      <c r="D53" s="47" t="s">
+      <c r="D53" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="47" t="s">
-        <v>301</v>
-      </c>
-      <c r="C54" s="47">
+      <c r="B54" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="C54" s="44">
         <v>19.02</v>
       </c>
-      <c r="D54" s="47" t="s">
+      <c r="D54" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
-      <c r="H54" s="47"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="47"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="47"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="47"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="47"/>
-      <c r="G56" s="47"/>
-      <c r="H56" s="47"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="47"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="47"/>
-      <c r="H57" s="47"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="47"/>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="47"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3497,15 +4015,15 @@
   <sheetData>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L2" t="s">
-        <v>224</v>
-      </c>
-      <c r="M2" s="49"/>
-      <c r="N2" s="23"/>
+        <v>220</v>
+      </c>
+      <c r="M2" s="46"/>
+      <c r="N2" s="20"/>
       <c r="O2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -3513,7 +4031,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -3523,10 +4041,10 @@
       <c r="B4" t="s">
         <v>82</v>
       </c>
-      <c r="P4" s="50"/>
+      <c r="P4" s="47"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="N5" s="50"/>
+      <c r="N5" s="47"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
@@ -3542,11 +4060,11 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D8" s="5"/>
-      <c r="P8" s="24" t="s">
+      <c r="P8" s="21" t="s">
         <v>59</v>
       </c>
       <c r="Q8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -3568,7 +4086,7 @@
       <c r="I9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="22" t="s">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="s">
@@ -3580,14 +4098,14 @@
       <c r="N9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="O9" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="24" t="s">
+      <c r="P9" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="Q9" s="22" t="s">
-        <v>119</v>
+      <c r="Q9" s="19" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -3609,7 +4127,7 @@
       <c r="I10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="22" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="4" t="s">
@@ -3621,14 +4139,14 @@
       <c r="N10" s="4">
         <v>20</v>
       </c>
-      <c r="O10" s="25" t="s">
+      <c r="O10" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="P10" s="26" t="s">
+      <c r="P10" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" s="27" t="s">
-        <v>117</v>
+      <c r="Q10" s="24" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -3650,7 +4168,7 @@
       <c r="I11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="22" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="4" t="s">
@@ -3662,7 +4180,7 @@
       <c r="N11" s="4">
         <v>30</v>
       </c>
-      <c r="O11" s="25" t="s">
+      <c r="O11" s="22" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3685,7 +4203,7 @@
       <c r="I12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="22" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -3697,7 +4215,7 @@
       <c r="N12" s="4">
         <v>60</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="O12" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3742,11 +4260,11 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="J16" s="50"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
@@ -3765,7 +4283,7 @@
         <v>44</v>
       </c>
       <c r="T17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
@@ -3776,7 +4294,7 @@
         <v>55</v>
       </c>
       <c r="T18" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
@@ -3790,7 +4308,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>8</v>
@@ -3805,7 +4323,7 @@
         <v>58</v>
       </c>
       <c r="T19" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
@@ -3860,7 +4378,7 @@
         <v>64</v>
       </c>
       <c r="T21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
@@ -3953,11 +4471,11 @@
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="N27" s="50" t="s">
+      <c r="N27" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="O27" s="50" t="s">
-        <v>267</v>
+      <c r="O27" s="47" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
@@ -3968,7 +4486,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
@@ -4005,7 +4523,7 @@
         <v>2</v>
       </c>
       <c r="O31" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
@@ -4016,8 +4534,8 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="23" t="s">
-        <v>205</v>
+      <c r="G32" s="20" t="s">
+        <v>201</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -4042,56 +4560,56 @@
         <v>3</v>
       </c>
       <c r="O34" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>308</v>
-      </c>
-      <c r="G35" s="56"/>
-      <c r="N35" s="54">
+        <v>304</v>
+      </c>
+      <c r="G35" s="53"/>
+      <c r="N35" s="51">
         <v>2</v>
       </c>
-      <c r="O35" s="54" t="s">
+      <c r="O35" s="51" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>309</v>
-      </c>
-      <c r="G36" s="56"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="47"/>
+        <v>305</v>
+      </c>
+      <c r="G36" s="53"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="I37" s="47"/>
-      <c r="J37" s="47"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="I38" s="47"/>
-      <c r="J38" s="47"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="I39" s="47"/>
-      <c r="J39" s="47"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="I40" s="47"/>
-      <c r="J40" s="47"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="I41" s="47"/>
-      <c r="J41" s="47"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4121,8 +4639,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F2" s="18" t="s">
-        <v>303</v>
+      <c r="F2" s="15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -4130,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -4148,110 +4707,110 @@
         <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="M4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="M5" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="N5" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="55" t="s">
+      <c r="O5" s="52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F6" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="I5" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="J5" s="55" t="s">
-        <v>241</v>
-      </c>
-      <c r="K5" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="L5" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="M5" s="55" t="s">
-        <v>305</v>
-      </c>
-      <c r="N5" s="55" t="s">
-        <v>252</v>
-      </c>
-      <c r="O5" s="55" t="s">
+      <c r="G6" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="53" t="s">
-        <v>257</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L6" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>14</v>
@@ -4259,7 +4818,7 @@
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -4269,56 +4828,56 @@
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="53" t="s">
-        <v>247</v>
+      <c r="K7" s="50" t="s">
+        <v>243</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>229</v>
+        <v>255</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>225</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="E8" s="53" t="s">
+      <c r="D8" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="50" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -4330,70 +4889,70 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="53" t="s">
-        <v>256</v>
+      <c r="B9" s="50" t="s">
+        <v>252</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="53" t="s">
-        <v>248</v>
+      <c r="L9" s="50" t="s">
+        <v>244</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="53" t="s">
-        <v>255</v>
+      <c r="B10" s="50" t="s">
+        <v>251</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="53"/>
+      <c r="D10" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" s="50"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="53" t="s">
-        <v>254</v>
+      <c r="B11" s="50" t="s">
+        <v>250</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="E11" s="53"/>
+      <c r="D11" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="E11" s="50"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="H11" s="53" t="s">
-        <v>240</v>
+      <c r="G11" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>236</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -4412,10 +4971,10 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="I12" s="53"/>
+      <c r="H12" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="I12" s="50"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -4551,14 +5110,14 @@
       <c r="O20" s="2"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C23" s="63" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="54" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24"/>
-      <c r="C24" s="23" t="s">
-        <v>311</v>
+      <c r="C24" s="20" t="s">
+        <v>307</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -4575,171 +5134,171 @@
       <c r="Q24"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="20" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C27" s="54" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C28" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C29" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C31" s="54" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C27" s="63" t="s">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C32" s="20" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C28" s="23" t="s">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C33" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
-      <c r="P28" s="47"/>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C29" s="23" t="s">
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C35" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C31" s="63" t="s">
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="20" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C32" s="23" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C33" s="23" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="63" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C36" s="23" t="s">
-        <v>320</v>
-      </c>
-    </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="23"/>
+      <c r="C37" s="20"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="23" t="s">
-        <v>329</v>
+      <c r="C38" s="20" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="47"/>
-      <c r="C39" s="65" t="s">
-        <v>330</v>
-      </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G40" s="47"/>
-      <c r="H40" s="47"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G41" s="47"/>
-      <c r="H41" s="47"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
-      <c r="H54" s="47"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="47"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="47"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="47"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="47"/>
-      <c r="G56" s="47"/>
-      <c r="H56" s="47"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="47"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="47"/>
-      <c r="H57" s="47"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="47"/>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="47"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4749,6 +5308,1106 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B2:T47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" style="63" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="63" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="63" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" style="63" customWidth="1"/>
+    <col min="5" max="5" width="24" style="63" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" style="63" customWidth="1"/>
+    <col min="7" max="7" width="29.85546875" style="63" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" style="63" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" style="63" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" style="63" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" style="63" customWidth="1"/>
+    <col min="12" max="12" width="26" style="63" customWidth="1"/>
+    <col min="13" max="13" width="27.7109375" style="63" customWidth="1"/>
+    <col min="14" max="14" width="30.85546875" style="63" customWidth="1"/>
+    <col min="15" max="17" width="22.7109375" style="63" customWidth="1"/>
+    <col min="18" max="18" width="24.140625" style="63" customWidth="1"/>
+    <col min="19" max="19" width="35.140625" style="63" customWidth="1"/>
+    <col min="20" max="20" width="21.5703125" style="63" customWidth="1"/>
+    <col min="21" max="22" width="12.7109375" style="63" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="63"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B2" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="D3" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="D5" s="71" t="s">
+        <v>437</v>
+      </c>
+      <c r="E5" s="71" t="s">
+        <v>358</v>
+      </c>
+      <c r="F5" s="71" t="s">
+        <v>365</v>
+      </c>
+      <c r="G5" s="71" t="s">
+        <v>373</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>380</v>
+      </c>
+      <c r="I5" s="71" t="s">
+        <v>418</v>
+      </c>
+      <c r="J5" s="71" t="s">
+        <v>387</v>
+      </c>
+      <c r="K5" s="71" t="s">
+        <v>395</v>
+      </c>
+      <c r="L5" s="71" t="s">
+        <v>398</v>
+      </c>
+      <c r="M5" s="71" t="s">
+        <v>401</v>
+      </c>
+      <c r="N5" s="71" t="s">
+        <v>412</v>
+      </c>
+      <c r="O5" s="71" t="s">
+        <v>427</v>
+      </c>
+      <c r="P5" s="71" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q5" s="71" t="s">
+        <v>436</v>
+      </c>
+      <c r="R5" s="71" t="s">
+        <v>446</v>
+      </c>
+      <c r="S5" s="71" t="s">
+        <v>450</v>
+      </c>
+      <c r="T5" s="52" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>341</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F6" s="71" t="s">
+        <v>366</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="M6" s="71" t="s">
+        <v>402</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q6" s="71" t="s">
+        <v>438</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="S6" s="71" t="s">
+        <v>451</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="73" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" s="72" t="s">
+        <v>344</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="71" t="s">
+        <v>367</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="N7" s="66"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="R7" s="73" t="s">
+        <v>448</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" s="72" t="s">
+        <v>361</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="75" t="s">
+        <v>377</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="N8" s="66"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="73" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="73"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="73" t="s">
+        <v>374</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="73" t="s">
+        <v>453</v>
+      </c>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="50"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="50"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="50" t="s">
+        <v>414</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I11" s="73" t="s">
+        <v>425</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="73"/>
+      <c r="Q11" s="73"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="73"/>
+      <c r="T11" s="73"/>
+    </row>
+    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="H12" s="73" t="s">
+        <v>392</v>
+      </c>
+      <c r="I12" s="73" t="s">
+        <v>424</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="73"/>
+      <c r="R12" s="73"/>
+      <c r="S12" s="73"/>
+      <c r="T12" s="73"/>
+    </row>
+    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="14"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+    </row>
+    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+    </row>
+    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+    </row>
+    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+    </row>
+    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+    </row>
+    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+    </row>
+    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+    </row>
+    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="66"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="I21" s="63" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="I22" s="63" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="I23" s="63" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="I24" s="65" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B25" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="J25" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="K25" s="68"/>
+      <c r="N25" s="63" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B26" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="I26" s="67" t="s">
+        <v>340</v>
+      </c>
+      <c r="J26" s="63" t="s">
+        <v>341</v>
+      </c>
+      <c r="K26" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="L26" s="63" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B27" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="F27" s="19">
+        <v>1</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19">
+        <v>1</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="K27" s="63">
+        <v>0</v>
+      </c>
+      <c r="L27" s="63" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B28" s="63" t="s">
+        <v>335</v>
+      </c>
+      <c r="F28" s="19">
+        <v>2</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19">
+        <v>2</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="K28" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B29" s="64" t="s">
+        <v>330</v>
+      </c>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19">
+        <v>3</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="K29" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F30" s="63" t="s">
+        <v>364</v>
+      </c>
+      <c r="I30" s="19">
+        <v>4</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="K30" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F31" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="I31" s="19">
+        <v>5</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="K31" s="63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F32" s="19">
+        <v>1</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="H32" s="74" t="s">
+        <v>368</v>
+      </c>
+      <c r="I32" s="19">
+        <v>6</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="K32" s="63">
+        <v>1</v>
+      </c>
+      <c r="L32" s="63" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="76" t="s">
+        <v>400</v>
+      </c>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="19">
+        <v>1</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="H33" s="74" t="s">
+        <v>370</v>
+      </c>
+      <c r="I33" s="19">
+        <v>7</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="K33" s="63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="78" t="s">
+        <v>401</v>
+      </c>
+      <c r="C34" s="78" t="s">
+        <v>402</v>
+      </c>
+      <c r="D34" s="78" t="s">
+        <v>403</v>
+      </c>
+      <c r="E34" s="78" t="s">
+        <v>404</v>
+      </c>
+      <c r="F34" s="19">
+        <v>1</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="H34" s="74" t="s">
+        <v>369</v>
+      </c>
+      <c r="I34" s="19">
+        <v>8</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="K34" s="63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="80">
+        <v>1</v>
+      </c>
+      <c r="C35" s="80" t="s">
+        <v>405</v>
+      </c>
+      <c r="D35" s="80" t="s">
+        <v>277</v>
+      </c>
+      <c r="E35" s="82" t="s">
+        <v>406</v>
+      </c>
+      <c r="I35" s="19">
+        <v>9</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="K35" s="63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="80">
+        <v>1</v>
+      </c>
+      <c r="C36" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="80" t="s">
+        <v>277</v>
+      </c>
+      <c r="E36" s="82" t="s">
+        <v>406</v>
+      </c>
+      <c r="I36" s="19">
+        <v>10</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="K36" s="63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="80">
+        <v>1</v>
+      </c>
+      <c r="C37" s="80" t="s">
+        <v>407</v>
+      </c>
+      <c r="D37" s="80" t="s">
+        <v>279</v>
+      </c>
+      <c r="E37" s="80"/>
+      <c r="H37" s="19"/>
+      <c r="J37" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="K37" s="70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="80">
+        <v>2</v>
+      </c>
+      <c r="C38" s="80" t="s">
+        <v>405</v>
+      </c>
+      <c r="D38" s="80" t="s">
+        <v>279</v>
+      </c>
+      <c r="E38" s="82" t="s">
+        <v>406</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="80">
+        <v>2</v>
+      </c>
+      <c r="C39" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="80" t="s">
+        <v>408</v>
+      </c>
+      <c r="E39" s="82" t="s">
+        <v>406</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="G39" s="67" t="s">
+        <v>355</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="80">
+        <v>2</v>
+      </c>
+      <c r="C40" s="80" t="s">
+        <v>407</v>
+      </c>
+      <c r="D40" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="E40" s="80"/>
+      <c r="F40" s="19">
+        <v>1</v>
+      </c>
+      <c r="G40" s="19">
+        <v>1</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="I40" s="19">
+        <v>220</v>
+      </c>
+      <c r="J40" s="19">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="80">
+        <v>2</v>
+      </c>
+      <c r="C41" s="80" t="s">
+        <v>410</v>
+      </c>
+      <c r="D41" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="E41" s="80"/>
+      <c r="F41" s="19">
+        <v>1</v>
+      </c>
+      <c r="G41" s="19">
+        <v>1</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="I41" s="19">
+        <v>230</v>
+      </c>
+      <c r="J41" s="19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="19">
+        <v>1</v>
+      </c>
+      <c r="G42" s="19">
+        <v>2</v>
+      </c>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19">
+        <v>200</v>
+      </c>
+      <c r="J42" s="19">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="19">
+        <v>1</v>
+      </c>
+      <c r="G43" s="19">
+        <v>3</v>
+      </c>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="79"/>
+      <c r="C44" s="79"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="79"/>
+      <c r="F44" s="19">
+        <v>1</v>
+      </c>
+      <c r="G44" s="19">
+        <v>5</v>
+      </c>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F45" s="19">
+        <v>2</v>
+      </c>
+      <c r="G45" s="19">
+        <v>6</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F46" s="19">
+        <v>2</v>
+      </c>
+      <c r="G46" s="19">
+        <v>9</v>
+      </c>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F47" s="19">
+        <v>2</v>
+      </c>
+      <c r="G47" s="19">
+        <v>10</v>
+      </c>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J25:K25"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H32" r:id="rId1" xr:uid="{1A8A6682-DD81-47D1-AB9E-2DE37B892992}"/>
+    <hyperlink ref="H33" r:id="rId2" display="file://img01" xr:uid="{C4277D61-7D78-4BA6-BF9D-25C2C7404285}"/>
+    <hyperlink ref="H34" r:id="rId3" display="file://img01" xr:uid="{274F48BA-EC95-4552-8937-B1BFFA7C1EDC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:AJ77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4776,13 +6435,13 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="T4" s="19" t="s">
+      <c r="T4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="19"/>
+      <c r="U4" s="16"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
@@ -4844,7 +6503,7 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>24</v>
@@ -4912,20 +6571,20 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="P10" s="20" t="s">
+      <c r="C10" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="P10" s="17" t="s">
         <v>83</v>
       </c>
       <c r="T10" s="4" t="s">
@@ -4943,7 +6602,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>84</v>
@@ -4983,18 +6642,18 @@
       </c>
       <c r="R13" s="5"/>
       <c r="T13" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>229</v>
+      <c r="E14" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>225</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>86</v>
@@ -5017,14 +6676,14 @@
       <c r="D15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="64" t="s">
-        <v>229</v>
+      <c r="E15" s="55" t="s">
+        <v>225</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>38</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="T15" t="s">
         <v>91</v>
@@ -5040,14 +6699,14 @@
       <c r="D16" s="4">
         <v>20</v>
       </c>
-      <c r="E16" s="28" t="s">
-        <v>323</v>
+      <c r="E16" s="25" t="s">
+        <v>319</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
@@ -5070,14 +6729,14 @@
       <c r="D17" s="4">
         <v>30</v>
       </c>
-      <c r="E17" s="28" t="s">
-        <v>323</v>
+      <c r="E17" s="25" t="s">
+        <v>319</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="2:35" x14ac:dyDescent="0.25">
@@ -5090,34 +6749,34 @@
       <c r="D18" s="4">
         <v>60</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="I18" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="T18" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="T18" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D19" s="4">
         <v>60</v>
       </c>
-      <c r="E19" s="28" t="s">
-        <v>325</v>
+      <c r="E19" s="25" t="s">
+        <v>321</v>
       </c>
       <c r="P19" s="62" t="s">
         <v>11</v>
@@ -5180,7 +6839,7 @@
     </row>
     <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="P22" s="4">
         <v>2</v>
@@ -5203,10 +6862,10 @@
       </c>
     </row>
     <row r="23" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="D23" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="J23" s="30" t="s">
+      <c r="D23" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="J23" s="27" t="s">
         <v>67</v>
       </c>
       <c r="P23" s="4">
@@ -5221,24 +6880,24 @@
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
       <c r="AG23" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AH23" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AI23" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="K24" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
+        <v>126</v>
+      </c>
+      <c r="K24" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
       <c r="P24" s="4">
         <v>4</v>
       </c>
@@ -5259,89 +6918,89 @@
         <v>105</v>
       </c>
       <c r="AG24" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AH24" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D25" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J25" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="K25" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="33"/>
+        <v>128</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="L25" s="32"/>
+      <c r="M25" s="30"/>
     </row>
     <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D26" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J26" s="31" t="s">
         <v>126</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D27" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J27" s="31" t="s">
-        <v>125</v>
+        <v>142</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D28" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="T28" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="U28" s="21"/>
-      <c r="X28" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y28" s="21"/>
-      <c r="AA28" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="T28" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="U28" s="18"/>
+      <c r="X28" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y28" s="18"/>
+      <c r="AA28" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="AD28" s="45" t="s">
+      <c r="AD28" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="AF28" s="19" t="s">
+      <c r="AF28" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="C29" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="P29" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="T29" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="U29" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="V29" s="28" t="s">
-        <v>158</v>
+      <c r="C29" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="P29" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="T29" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="U29" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="V29" s="25" t="s">
+        <v>154</v>
       </c>
       <c r="X29" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AA29" s="41" t="s">
+      <c r="AA29" s="38" t="s">
         <v>20</v>
       </c>
       <c r="AB29" s="4" t="s">
@@ -5350,111 +7009,111 @@
       <c r="AC29" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AD29" s="43" t="s">
+      <c r="AD29" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="AF29" s="41" t="s">
+      <c r="AF29" s="38" t="s">
         <v>9</v>
       </c>
       <c r="AG29" s="4" t="s">
         <v>21</v>
       </c>
       <c r="AH29" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI29" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="AI29" s="38" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="30" spans="2:35" x14ac:dyDescent="0.25">
       <c r="C30" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="25" t="s">
-        <v>128</v>
-      </c>
       <c r="H30" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I30" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="T30" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="U30" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="V30" s="25">
+        <v>5</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y30" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="I30" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="T30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="U30" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="V30" s="28">
-        <v>5</v>
-      </c>
-      <c r="X30" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y30" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AA30" s="42" t="s">
+      <c r="AA30" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AB30" s="40" t="s">
-        <v>192</v>
+      <c r="AB30" s="37" t="s">
+        <v>188</v>
       </c>
       <c r="AC30" s="4">
         <v>225</v>
       </c>
-      <c r="AD30" s="42" t="s">
+      <c r="AD30" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="AF30" s="42" t="s">
+      <c r="AF30" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="AG30" s="40" t="s">
-        <v>196</v>
+      <c r="AG30" s="37" t="s">
+        <v>192</v>
       </c>
       <c r="AH30" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="AI30" s="42" t="s">
-        <v>216</v>
+        <v>195</v>
+      </c>
+      <c r="AI30" s="39" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="C31" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="46" t="s">
+      <c r="C31" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="46">
+      <c r="E31" s="43">
         <v>8</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H31" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="I31" s="46" t="s">
-        <v>133</v>
+        <v>126</v>
+      </c>
+      <c r="H31" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="I31" s="43" t="s">
+        <v>129</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="4" t="s">
         <v>34</v>
@@ -5462,67 +7121,67 @@
       <c r="R31" s="3">
         <v>7.8</v>
       </c>
-      <c r="T31" s="28" t="s">
+      <c r="T31" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="U31" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="V31" s="25">
+        <v>6</v>
+      </c>
+      <c r="X31" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y31" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="U31" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="V31" s="28">
-        <v>6</v>
-      </c>
-      <c r="X31" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y31" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA31" s="42" t="s">
+      <c r="AA31" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="AB31" s="40" t="s">
-        <v>193</v>
+      <c r="AB31" s="37" t="s">
+        <v>189</v>
       </c>
       <c r="AC31" s="4">
         <v>0</v>
       </c>
-      <c r="AD31" s="42" t="s">
+      <c r="AD31" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AF31" s="42" t="s">
+      <c r="AF31" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AG31" s="40" t="s">
-        <v>197</v>
+      <c r="AG31" s="37" t="s">
+        <v>193</v>
       </c>
       <c r="AH31" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="AI31" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI31" s="39" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="C32" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" s="46" t="s">
+      <c r="C32" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="46">
+      <c r="E32" s="43">
         <v>6</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H32" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="I32" s="46" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="H32" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" s="43" t="s">
+        <v>130</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="Q32" s="4" t="s">
         <v>35</v>
@@ -5530,67 +7189,67 @@
       <c r="R32" s="3">
         <v>8</v>
       </c>
-      <c r="T32" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="U32" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="V32" s="28">
+      <c r="T32" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="U32" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="V32" s="25">
         <v>7</v>
       </c>
       <c r="X32" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y32" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="Y32" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA32" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB32" s="40" t="s">
-        <v>194</v>
+      <c r="AA32" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB32" s="37" t="s">
+        <v>190</v>
       </c>
       <c r="AC32" s="4">
         <v>125</v>
       </c>
-      <c r="AD32" s="42" t="s">
+      <c r="AD32" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="AF32" s="42" t="s">
+      <c r="AF32" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="AG32" s="40" t="s">
-        <v>198</v>
+      <c r="AG32" s="37" t="s">
+        <v>194</v>
       </c>
       <c r="AH32" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI32" s="42" t="s">
-        <v>216</v>
+        <v>197</v>
+      </c>
+      <c r="AI32" s="39" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="43">
+        <v>9</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="46">
-        <v>9</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H33" s="46" t="s">
+      <c r="I33" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="46" t="s">
-        <v>135</v>
-      </c>
       <c r="P33" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="4" t="s">
         <v>36</v>
@@ -5598,98 +7257,98 @@
       <c r="R33" s="3">
         <v>9.5</v>
       </c>
-      <c r="T33" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="U33" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="V33" s="28">
+      <c r="T33" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="U33" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="V33" s="25">
         <v>5</v>
       </c>
-      <c r="AA33" s="42" t="s">
+      <c r="AA33" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB33" s="37" t="s">
         <v>191</v>
-      </c>
-      <c r="AB33" s="40" t="s">
-        <v>195</v>
       </c>
       <c r="AC33" s="4">
         <v>220</v>
       </c>
-      <c r="AD33" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF33" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="AG33" s="40" t="s">
+      <c r="AD33" s="39" t="s">
         <v>198</v>
       </c>
+      <c r="AF33" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="AG33" s="37" t="s">
+        <v>194</v>
+      </c>
       <c r="AH33" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="AI33" s="42" t="s">
-        <v>191</v>
+        <v>199</v>
+      </c>
+      <c r="AI33" s="39" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C34" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" s="46">
+      <c r="C34" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" s="43">
         <v>7</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R34" s="3">
         <v>2</v>
       </c>
-      <c r="T34" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="U34" s="36" t="s">
+      <c r="T34" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="V34" s="28">
+      <c r="U34" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="V34" s="25">
         <v>9</v>
       </c>
     </row>
     <row r="35" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C35" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="46">
+      <c r="C35" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="43">
         <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="R35" s="3">
         <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="37" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C37" s="32" t="s">
-        <v>151</v>
+      <c r="C37" s="29" t="s">
+        <v>147</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -5700,8 +7359,8 @@
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
-      <c r="P37" s="32" t="s">
-        <v>211</v>
+      <c r="P37" s="29" t="s">
+        <v>207</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -5710,7 +7369,7 @@
       <c r="U37" s="9"/>
       <c r="V37" s="9"/>
       <c r="AA37" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -5724,178 +7383,178 @@
     </row>
     <row r="38" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="P38" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AA38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="P39" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AA39" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="P40" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AA40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA41" s="48" t="s">
-        <v>145</v>
+        <v>132</v>
+      </c>
+      <c r="AA41" s="45" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA42" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB42" s="44"/>
-      <c r="AC42" s="44"/>
-      <c r="AD42" s="44"/>
-      <c r="AE42" s="44"/>
-      <c r="AF42" s="44"/>
-      <c r="AG42" s="44"/>
-      <c r="AH42" s="44"/>
+        <v>135</v>
+      </c>
+      <c r="AA42" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB42" s="41"/>
+      <c r="AC42" s="41"/>
+      <c r="AD42" s="41"/>
+      <c r="AE42" s="41"/>
+      <c r="AF42" s="41"/>
+      <c r="AG42" s="41"/>
+      <c r="AH42" s="41"/>
     </row>
     <row r="43" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>145</v>
-      </c>
-      <c r="O44" s="29" t="s">
-        <v>159</v>
+        <v>141</v>
+      </c>
+      <c r="O44" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="T44" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Y44" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>141</v>
-      </c>
-      <c r="O45" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="O45" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="P45" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q45" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="R45" s="28" t="s">
-        <v>161</v>
+      <c r="P45" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q45" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="R45" s="25" t="s">
+        <v>157</v>
       </c>
       <c r="T45" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="U45" t="s">
         <v>7</v>
       </c>
       <c r="V45" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Y45" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N46" t="s">
-        <v>175</v>
-      </c>
-      <c r="O46" s="28">
+        <v>171</v>
+      </c>
+      <c r="O46" s="25">
         <v>1</v>
       </c>
-      <c r="P46" s="28">
+      <c r="P46" s="25">
         <v>1</v>
       </c>
-      <c r="Q46" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="R46" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="T46" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="U46" s="28">
+      <c r="Q46" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="R46" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="T46" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="U46" s="25">
         <v>1</v>
       </c>
-      <c r="V46" s="28">
+      <c r="V46" s="25">
         <v>8</v>
       </c>
       <c r="Y46" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AE46" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
-        <v>218</v>
-      </c>
-      <c r="O47" s="28">
+        <v>214</v>
+      </c>
+      <c r="O47" s="25">
         <v>2</v>
       </c>
-      <c r="P47" s="28">
+      <c r="P47" s="25">
         <v>2</v>
       </c>
-      <c r="Q47" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="R47" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="T47" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="U47" s="28">
+      <c r="Q47" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="R47" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="T47" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="U47" s="25">
         <v>2</v>
       </c>
-      <c r="V47" s="28">
+      <c r="V47" s="25">
         <v>8</v>
       </c>
       <c r="Y47" t="s">
         <v>58</v>
       </c>
       <c r="AF47" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C48" s="58" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D48" s="59"/>
       <c r="E48" s="59"/>
@@ -5904,37 +7563,37 @@
       <c r="H48" s="59"/>
       <c r="I48" s="59"/>
       <c r="J48" s="59"/>
-      <c r="O48" s="28">
+      <c r="O48" s="25">
         <v>3</v>
       </c>
-      <c r="P48" s="28">
+      <c r="P48" s="25">
         <v>3</v>
       </c>
-      <c r="Q48" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="R48" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="T48" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="U48" s="28">
+      <c r="Q48" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="R48" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="T48" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="U48" s="25">
         <v>1</v>
       </c>
-      <c r="V48" s="28">
+      <c r="V48" s="25">
         <v>9</v>
       </c>
-      <c r="AE48" s="41" t="s">
+      <c r="AE48" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="AF48" s="42" t="s">
+      <c r="AF48" s="39" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="49" spans="3:32" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="60" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D49" s="60"/>
       <c r="E49" s="60"/>
@@ -5943,354 +7602,354 @@
       <c r="H49" s="60"/>
       <c r="I49" s="60"/>
       <c r="J49" s="60"/>
-      <c r="O49" s="28">
+      <c r="O49" s="25">
         <v>4</v>
       </c>
-      <c r="P49" s="28">
+      <c r="P49" s="25">
         <v>4</v>
       </c>
-      <c r="Q49" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="R49" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="T49" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="U49" s="28">
+      <c r="Q49" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="T49" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="U49" s="25">
         <v>1</v>
       </c>
-      <c r="V49" s="28">
+      <c r="V49" s="25">
         <v>9</v>
       </c>
-      <c r="AE49" s="42" t="s">
+      <c r="AE49" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AF49" s="42" t="s">
+      <c r="AF49" s="39" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O50" s="28">
+      <c r="O50" s="25">
         <v>5</v>
       </c>
-      <c r="P50" s="28">
+      <c r="P50" s="25">
         <v>5</v>
       </c>
-      <c r="Q50" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="R50" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="AE50" s="42" t="s">
+      <c r="Q50" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="R50" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE50" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="AF50" s="42" t="s">
+      <c r="AF50" s="39" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="51" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O51" s="28">
+      <c r="O51" s="25">
         <v>6</v>
       </c>
-      <c r="P51" s="28">
+      <c r="P51" s="25">
         <v>6</v>
       </c>
-      <c r="Q51" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="R51" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE51" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF51" s="42" t="s">
+      <c r="Q51" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="R51" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE51" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF51" s="39" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="52" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C52" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="H52" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="O52" s="28">
+      <c r="C52" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O52" s="25">
         <v>7</v>
       </c>
-      <c r="P52" s="28">
+      <c r="P52" s="25">
         <v>7</v>
       </c>
-      <c r="Q52" s="39" t="s">
+      <c r="Q52" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="R52" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="R52" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="AE52" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="AF52" s="42" t="s">
-        <v>202</v>
+      <c r="AE52" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="AF52" s="39" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C53" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F53" t="s">
+        <v>124</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I53" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" t="s">
+        <v>117</v>
+      </c>
+      <c r="O53" s="25">
+        <v>8</v>
+      </c>
+      <c r="P53" s="25">
+        <v>8</v>
+      </c>
+      <c r="Q53" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="R53" s="36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C54" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" s="43">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>126</v>
+      </c>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="O54" s="25">
+        <v>9</v>
+      </c>
+      <c r="P54" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="R54" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C55" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="46" t="s">
+      <c r="D55" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="43">
+        <v>6</v>
+      </c>
+      <c r="F55" t="s">
+        <v>126</v>
+      </c>
+      <c r="H55" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="I55" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="J55" t="s">
+        <v>122</v>
+      </c>
+      <c r="N55" t="s">
+        <v>172</v>
+      </c>
+      <c r="O55" s="25">
+        <v>10</v>
+      </c>
+      <c r="P55" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q55" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="R55" s="36" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C56" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="D56" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="E56" s="43">
+        <v>9</v>
+      </c>
+      <c r="F56" t="s">
         <v>128</v>
       </c>
-      <c r="H53" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="I53" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="J53" t="s">
+      <c r="H56" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="I56" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="J56" t="s">
         <v>121</v>
       </c>
-      <c r="O53" s="28">
+      <c r="O56" s="25">
+        <v>11</v>
+      </c>
+      <c r="P56" s="25">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="R56" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C57" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" s="43">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
+        <v>127</v>
+      </c>
+      <c r="O57" s="25">
+        <v>12</v>
+      </c>
+      <c r="P57" s="25">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="R57" s="36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C58" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="E58" s="43">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>128</v>
+      </c>
+      <c r="O58" s="25">
+        <v>13</v>
+      </c>
+      <c r="P58" s="25">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="R58" s="36" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="O59" s="25">
+        <v>14</v>
+      </c>
+      <c r="P59" s="25">
+        <v>6</v>
+      </c>
+      <c r="Q59" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="R59" s="36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="O60" s="25">
+        <v>15</v>
+      </c>
+      <c r="P60" s="25">
+        <v>7</v>
+      </c>
+      <c r="Q60" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="R60" s="36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="O61" s="25">
+        <v>16</v>
+      </c>
+      <c r="P61" s="25">
         <v>8</v>
       </c>
-      <c r="P53" s="28">
-        <v>8</v>
-      </c>
-      <c r="Q53" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="R53" s="39" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C54" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="D54" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="E54" s="46">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>130</v>
-      </c>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="O54" s="28">
-        <v>9</v>
-      </c>
-      <c r="P54" s="28">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="R54" s="39" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C55" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="46">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>130</v>
-      </c>
-      <c r="H55" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="I55" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="J55" t="s">
-        <v>126</v>
-      </c>
-      <c r="N55" t="s">
-        <v>176</v>
-      </c>
-      <c r="O55" s="28">
-        <v>10</v>
-      </c>
-      <c r="P55" s="28">
-        <v>2</v>
-      </c>
-      <c r="Q55" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="R55" s="39" t="s">
+      <c r="Q61" s="36" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C56" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="E56" s="46">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>132</v>
-      </c>
-      <c r="H56" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="I56" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="J56" t="s">
-        <v>125</v>
-      </c>
-      <c r="O56" s="28">
-        <v>11</v>
-      </c>
-      <c r="P56" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="R56" s="39" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C57" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="D57" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="E57" s="46">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>131</v>
-      </c>
-      <c r="O57" s="28">
-        <v>12</v>
-      </c>
-      <c r="P57" s="28">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="R57" s="39" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="C58" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="D58" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="E58" s="46">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>132</v>
-      </c>
-      <c r="O58" s="28">
-        <v>13</v>
-      </c>
-      <c r="P58" s="28">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="R58" s="39" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O59" s="28">
-        <v>14</v>
-      </c>
-      <c r="P59" s="28">
-        <v>6</v>
-      </c>
-      <c r="Q59" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="R59" s="39" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O60" s="28">
-        <v>15</v>
-      </c>
-      <c r="P60" s="28">
-        <v>7</v>
-      </c>
-      <c r="Q60" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="R60" s="39" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
-      <c r="O61" s="28">
-        <v>16</v>
-      </c>
-      <c r="P61" s="28">
-        <v>8</v>
-      </c>
-      <c r="Q61" s="39" t="s">
+      <c r="R61" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="R61" s="39" t="s">
-        <v>187</v>
-      </c>
     </row>
     <row r="71" spans="17:24" x14ac:dyDescent="0.25">
-      <c r="Q71" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="W71" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="X71" s="21"/>
+      <c r="Q71" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="W71" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="X71" s="18"/>
     </row>
     <row r="72" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q72" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="R72" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="T72" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="W72" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="X72" s="4" t="s">
         <v>39</v>
@@ -6298,7 +7957,7 @@
     </row>
     <row r="73" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q73" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="R73" s="4" t="s">
         <v>34</v>
@@ -6307,18 +7966,18 @@
         <v>7.8</v>
       </c>
       <c r="T73" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="W73" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="X73" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q74" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="R74" s="4" t="s">
         <v>35</v>
@@ -6327,18 +7986,18 @@
         <v>8</v>
       </c>
       <c r="T74" t="s">
+        <v>126</v>
+      </c>
+      <c r="W74" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="X74" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="W74" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="X74" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="75" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q75" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="R75" s="4" t="s">
         <v>36</v>
@@ -6347,35 +8006,35 @@
         <v>9.5</v>
       </c>
       <c r="T75" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="W75" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="X75" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="X75" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="76" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q76" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="R76" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="S76" s="3">
         <v>2</v>
       </c>
       <c r="T76" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q77" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R77" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="S77" s="3">
         <v>4.5999999999999996</v>
@@ -6395,309 +8054,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:N26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="7" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="18.28515625" customWidth="1"/>
-    <col min="15" max="22" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="4" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>